--- a/AAII_Financials/Quarterly/MOTNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOTNF_QTR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -882,7 +882,7 @@
         <v>4</v>
       </c>
       <c r="G14" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -953,7 +953,7 @@
         <v>2300</v>
       </c>
       <c r="H17" s="3">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="I17" s="3">
         <v>2200</v>
@@ -982,7 +982,7 @@
         <v>-2300</v>
       </c>
       <c r="H18" s="3">
-        <v>-5400</v>
+        <v>-5500</v>
       </c>
       <c r="I18" s="3">
         <v>-2200</v>
@@ -1053,10 +1053,10 @@
         <v>-4100</v>
       </c>
       <c r="H21" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="I21" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="J21" s="3">
         <v>-3500</v>
@@ -1111,10 +1111,10 @@
         <v>-4100</v>
       </c>
       <c r="H23" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="I23" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="J23" s="3">
         <v>-3500</v>
@@ -1198,10 +1198,10 @@
         <v>-4100</v>
       </c>
       <c r="H26" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="I26" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="J26" s="3">
         <v>-3500</v>
@@ -1227,10 +1227,10 @@
         <v>-4100</v>
       </c>
       <c r="H27" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="I27" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="J27" s="3">
         <v>-3500</v>
@@ -1401,10 +1401,10 @@
         <v>-4100</v>
       </c>
       <c r="H33" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="I33" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="J33" s="3">
         <v>-3500</v>
@@ -1459,10 +1459,10 @@
         <v>-4100</v>
       </c>
       <c r="H35" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="I35" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="J35" s="3">
         <v>-3500</v>
@@ -1670,7 +1670,7 @@
         <v>2200</v>
       </c>
       <c r="J45" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="K45" s="3">
         <v>1700</v>
@@ -1696,10 +1696,10 @@
         <v>2000</v>
       </c>
       <c r="I46" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="J46" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="K46" s="3">
         <v>4500</v>
@@ -1728,7 +1728,7 @@
         <v>3900</v>
       </c>
       <c r="J47" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="K47" s="3">
         <v>3900</v>
@@ -1925,13 +1925,13 @@
         <v>300</v>
       </c>
       <c r="H54" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="I54" s="3">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="J54" s="3">
-        <v>9100</v>
+        <v>9200</v>
       </c>
       <c r="K54" s="3">
         <v>9300</v>
@@ -1968,7 +1968,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="E57" s="3">
         <v>2500</v>
@@ -1983,7 +1983,7 @@
         <v>1000</v>
       </c>
       <c r="I57" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J57" s="3">
         <v>400</v>
@@ -2073,7 +2073,7 @@
         <v>700</v>
       </c>
       <c r="J60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K60" s="3">
         <v>600</v>
@@ -2247,7 +2247,7 @@
         <v>700</v>
       </c>
       <c r="J66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K66" s="3">
         <v>600</v>
@@ -2387,25 +2387,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-294400</v>
+        <v>-297300</v>
       </c>
       <c r="E72" s="3">
-        <v>-293400</v>
+        <v>-296400</v>
       </c>
       <c r="F72" s="3">
-        <v>-292300</v>
+        <v>-295200</v>
       </c>
       <c r="G72" s="3">
-        <v>-290700</v>
+        <v>-293600</v>
       </c>
       <c r="H72" s="3">
-        <v>-286600</v>
+        <v>-289500</v>
       </c>
       <c r="I72" s="3">
-        <v>-281100</v>
+        <v>-283900</v>
       </c>
       <c r="J72" s="3">
-        <v>-278900</v>
+        <v>-281700</v>
       </c>
       <c r="K72" s="3">
         <v>-275400</v>
@@ -2506,7 +2506,7 @@
         <v>-2800</v>
       </c>
       <c r="E76" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="F76" s="3">
         <v>-2000</v>
@@ -2515,7 +2515,7 @@
         <v>-1600</v>
       </c>
       <c r="H76" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="I76" s="3">
         <v>7700</v>
@@ -2607,10 +2607,10 @@
         <v>-4100</v>
       </c>
       <c r="H81" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="I81" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="J81" s="3">
         <v>-3500</v>
@@ -2823,7 +2823,7 @@
         <v>-100</v>
       </c>
       <c r="H89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I89" s="3">
         <v>-400</v>
@@ -3171,7 +3171,7 @@
         <v>-200</v>
       </c>
       <c r="I102" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="J102" s="3">
         <v>-100</v>
